--- a/events/Markkleeberg_2017_WC/Markkleeberg_2017_WC_start.xlsx
+++ b/events/Markkleeberg_2017_WC/Markkleeberg_2017_WC_start.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W579"/>
+  <dimension ref="A1:AC579"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,17 +519,47 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Name4</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Name5</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Name6</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
           <t>ICF_ID1</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ICF_ID2</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ICF_ID3</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ICF_ID4</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ICF_ID5</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ICF_ID6</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1307,12 @@
           <t>HEGER Vojtech</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>42007</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>68872</t>
         </is>
@@ -1345,12 +1375,12 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -1413,12 +1443,12 @@
           <t>MUELLER Kevin</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>35148</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>35149</t>
         </is>
@@ -1481,12 +1511,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>35368</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -1549,12 +1579,12 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>35145</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -1617,12 +1647,12 @@
           <t>BENZIEN Jan</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>35134</t>
         </is>
@@ -1685,12 +1715,12 @@
           <t>CAILHOL Hugo</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>35476</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>35491</t>
         </is>
@@ -1753,12 +1783,12 @@
           <t>BISO Hugo</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>35403</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>35229</t>
         </is>
@@ -1821,12 +1851,12 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>35060</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -1889,12 +1919,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -1957,12 +1987,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -2025,12 +2055,12 @@
           <t>SKANTAR Peter</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>35360</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>35361</t>
         </is>
@@ -2093,12 +2123,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -2209,7 +2239,7 @@
           <t>MOURYA Champa</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>68933</t>
         </is>
@@ -2267,7 +2297,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -2325,7 +2355,7 @@
           <t>DELASSUS Marjorie</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>71964</t>
         </is>
@@ -2383,7 +2413,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -2441,7 +2471,7 @@
           <t>TRETIAKOVA Svetlana</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>68775</t>
         </is>
@@ -2499,7 +2529,7 @@
           <t>MUKHGALEEVA Polina</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>35768</t>
         </is>
@@ -2557,7 +2587,7 @@
           <t>RIHOVA Eva</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>51791</t>
         </is>
@@ -2615,7 +2645,7 @@
           <t>HENRY Margaux</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>51995</t>
         </is>
@@ -2832,7 +2862,7 @@
           <t>DANIELS Haley</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>36260</t>
         </is>
@@ -2890,7 +2920,7 @@
           <t>OHMAYER Birgit</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>39157</t>
         </is>
@@ -2948,7 +2978,7 @@
           <t>SKACHOVA Monika</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>53078</t>
         </is>
@@ -3006,7 +3036,7 @@
           <t>SABITOVA Zulfia</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>40572</t>
         </is>
@@ -3064,7 +3094,7 @@
           <t>HERZOG Andrea</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>55099</t>
         </is>
@@ -3122,7 +3152,7 @@
           <t>GLEJTEKOVA Simona</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>55166</t>
         </is>
@@ -3180,7 +3210,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -3238,7 +3268,7 @@
           <t>MACEKOVA Simona</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>45153</t>
         </is>
@@ -3296,7 +3326,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -3354,7 +3384,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -3412,7 +3442,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -3523,7 +3553,7 @@
           <t>JANCOVA Monika</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>36015</t>
         </is>
@@ -3581,7 +3611,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -3639,7 +3669,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -3697,7 +3727,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -3755,7 +3785,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -3866,7 +3896,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -3924,7 +3954,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -3982,7 +4012,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -4040,7 +4070,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -4098,7 +4128,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -4156,7 +4186,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -4214,7 +4244,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -4272,7 +4302,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -4330,7 +4360,7 @@
           <t>VERMA Dharmendra</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>75387</t>
         </is>
@@ -4388,7 +4418,7 @@
           <t>KARLIVANS Toms</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>52325</t>
         </is>
@@ -4446,7 +4476,7 @@
           <t>CAPSTICK Finley</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>76710</t>
         </is>
@@ -4504,7 +4534,7 @@
           <t>KEER Kuldeep Singh</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>68932</t>
         </is>
@@ -4562,7 +4592,7 @@
           <t>KEER Dheeraj</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>68963</t>
         </is>
@@ -4620,7 +4650,7 @@
           <t>MCCREERY Alistair</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>60125</t>
         </is>
@@ -4678,7 +4708,7 @@
           <t>VIANELLO Marco</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>54910</t>
         </is>
@@ -4736,7 +4766,7 @@
           <t>PRIGENT Yves</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>35671</t>
         </is>
@@ -4794,7 +4824,7 @@
           <t>RAMRATTAN Darius</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>60059</t>
         </is>
@@ -4852,7 +4882,7 @@
           <t>THOMPSON Angus</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="X76" t="inlineStr">
         <is>
           <t>44814</t>
         </is>
@@ -4910,7 +4940,7 @@
           <t>KRIESINGER Ingo</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
+      <c r="X77" t="inlineStr">
         <is>
           <t>35336</t>
         </is>
@@ -4968,7 +4998,7 @@
           <t>FARRELL Oisin</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr">
+      <c r="X78" t="inlineStr">
         <is>
           <t>37916</t>
         </is>
@@ -5026,7 +5056,7 @@
           <t>SIMPSON Keenan</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr">
+      <c r="X79" t="inlineStr">
         <is>
           <t>71797</t>
         </is>
@@ -5084,7 +5114,7 @@
           <t>HAWTHORNE Alex</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr">
+      <c r="X80" t="inlineStr">
         <is>
           <t>51645</t>
         </is>
@@ -5142,7 +5172,7 @@
           <t>HENDRICK Noel</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr">
+      <c r="X81" t="inlineStr">
         <is>
           <t>43003</t>
         </is>
@@ -5200,7 +5230,7 @@
           <t>BOWERS Christopher</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr">
+      <c r="X82" t="inlineStr">
         <is>
           <t>52010</t>
         </is>
@@ -5258,7 +5288,7 @@
           <t>SOARES Renan</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr">
+      <c r="X83" t="inlineStr">
         <is>
           <t>42776</t>
         </is>
@@ -5316,7 +5346,7 @@
           <t>SAEKI Yutaro</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr">
+      <c r="X84" t="inlineStr">
         <is>
           <t>37678</t>
         </is>
@@ -5374,7 +5404,7 @@
           <t>WESTFALL Tyler</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
+      <c r="X85" t="inlineStr">
         <is>
           <t>51919</t>
         </is>
@@ -5432,7 +5462,7 @@
           <t>CORTEZ Geronimo</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
+      <c r="X86" t="inlineStr">
         <is>
           <t>51835</t>
         </is>
@@ -5490,7 +5520,7 @@
           <t>YOSHIDA Taku</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
+      <c r="X87" t="inlineStr">
         <is>
           <t>41611</t>
         </is>
@@ -5548,7 +5578,7 @@
           <t>ROSSI Lucas</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr">
+      <c r="X88" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
@@ -5606,7 +5636,7 @@
           <t>JAKSE Zan</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr">
+      <c r="X89" t="inlineStr">
         <is>
           <t>44340</t>
         </is>
@@ -5664,7 +5694,7 @@
           <t>POPE Benjamin</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr">
+      <c r="X90" t="inlineStr">
         <is>
           <t>51753</t>
         </is>
@@ -5722,7 +5752,7 @@
           <t>MUNSCH Manuel</t>
         </is>
       </c>
-      <c r="U91" t="inlineStr">
+      <c r="X91" t="inlineStr">
         <is>
           <t>35631</t>
         </is>
@@ -5780,7 +5810,7 @@
           <t>MAPELLI Guilherme Marcello</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
+      <c r="X92" t="inlineStr">
         <is>
           <t>38015</t>
         </is>
@@ -5838,7 +5868,7 @@
           <t>WAHLEN Fredrik</t>
         </is>
       </c>
-      <c r="U93" t="inlineStr">
+      <c r="X93" t="inlineStr">
         <is>
           <t>35102</t>
         </is>
@@ -5896,7 +5926,7 @@
           <t>WERRO Lukas</t>
         </is>
       </c>
-      <c r="U94" t="inlineStr">
+      <c r="X94" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
@@ -5954,7 +5984,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr">
+      <c r="X95" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -6012,7 +6042,7 @@
           <t>WEGER Matthias</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr">
+      <c r="X96" t="inlineStr">
         <is>
           <t>68837</t>
         </is>
@@ -6070,7 +6100,7 @@
           <t>POWELL Richard</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
+      <c r="X97" t="inlineStr">
         <is>
           <t>36444</t>
         </is>
@@ -6128,7 +6158,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
+      <c r="X98" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -6186,7 +6216,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
+      <c r="X99" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -6244,7 +6274,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
+      <c r="X100" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -6302,7 +6332,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U101" t="inlineStr">
+      <c r="X101" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -6360,7 +6390,7 @@
           <t>ADACHI Kazuya</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr">
+      <c r="X102" t="inlineStr">
         <is>
           <t>36646</t>
         </is>
@@ -6418,7 +6448,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr">
+      <c r="X103" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -6476,7 +6506,7 @@
           <t>SRABOTNIK Martin</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
+      <c r="X104" t="inlineStr">
         <is>
           <t>39080</t>
         </is>
@@ -6534,7 +6564,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U105" t="inlineStr">
+      <c r="X105" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -6592,7 +6622,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr">
+      <c r="X106" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -6650,7 +6680,7 @@
           <t>IVALDI Zeno</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr">
+      <c r="X107" t="inlineStr">
         <is>
           <t>35480</t>
         </is>
@@ -6708,7 +6738,7 @@
           <t>BRUS Simon</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr">
+      <c r="X108" t="inlineStr">
         <is>
           <t>39076</t>
         </is>
@@ -6766,7 +6796,7 @@
           <t>MALEK Andrej</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr">
+      <c r="X109" t="inlineStr">
         <is>
           <t>39246</t>
         </is>
@@ -6877,7 +6907,7 @@
           <t>LAUNAY Antoine</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr">
+      <c r="X111" t="inlineStr">
         <is>
           <t>68776</t>
         </is>
@@ -6935,7 +6965,7 @@
           <t>OKREGLAK Maciej</t>
         </is>
       </c>
-      <c r="U112" t="inlineStr">
+      <c r="X112" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
@@ -6993,7 +7023,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr">
+      <c r="X113" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -7051,7 +7081,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U114" t="inlineStr">
+      <c r="X114" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
@@ -7109,7 +7139,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr">
+      <c r="X115" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -7167,7 +7197,7 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr">
+      <c r="X116" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -7225,7 +7255,7 @@
           <t>COMBOT Sebastien</t>
         </is>
       </c>
-      <c r="U117" t="inlineStr">
+      <c r="X117" t="inlineStr">
         <is>
           <t>35234</t>
         </is>
@@ -7283,7 +7313,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr">
+      <c r="X118" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -7341,7 +7371,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr">
+      <c r="X119" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -7399,7 +7429,7 @@
           <t>GRIMM Alexander</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr">
+      <c r="X120" t="inlineStr">
         <is>
           <t>35112</t>
         </is>
@@ -7457,7 +7487,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U121" t="inlineStr">
+      <c r="X121" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -7515,7 +7545,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr">
+      <c r="X122" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -7573,7 +7603,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr">
+      <c r="X123" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -7631,7 +7661,7 @@
           <t>SCHUBERT Sebastian</t>
         </is>
       </c>
-      <c r="U124" t="inlineStr">
+      <c r="X124" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
@@ -7689,7 +7719,7 @@
           <t>HRADILEK Vavrinec</t>
         </is>
       </c>
-      <c r="U125" t="inlineStr">
+      <c r="X125" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
@@ -7747,7 +7777,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U126" t="inlineStr">
+      <c r="X126" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -7805,7 +7835,7 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U127" t="inlineStr">
+      <c r="X127" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -7863,7 +7893,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U128" t="inlineStr">
+      <c r="X128" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -7921,7 +7951,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U129" t="inlineStr">
+      <c r="X129" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -7979,7 +8009,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U130" t="inlineStr">
+      <c r="X130" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -8037,7 +8067,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr">
+      <c r="X131" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -8095,7 +8125,7 @@
           <t>AIGNER Hannes</t>
         </is>
       </c>
-      <c r="U132" t="inlineStr">
+      <c r="X132" t="inlineStr">
         <is>
           <t>35115</t>
         </is>
@@ -8153,7 +8183,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U133" t="inlineStr">
+      <c r="X133" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -8211,7 +8241,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr">
+      <c r="X134" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -8269,7 +8299,7 @@
           <t>BIAZIZZO Mathieu</t>
         </is>
       </c>
-      <c r="U135" t="inlineStr">
+      <c r="X135" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
@@ -8327,7 +8357,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U136" t="inlineStr">
+      <c r="X136" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -8385,7 +8415,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U137" t="inlineStr">
+      <c r="X137" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -8496,7 +8526,7 @@
           <t>MOURYA Champa</t>
         </is>
       </c>
-      <c r="U139" t="inlineStr">
+      <c r="X139" t="inlineStr">
         <is>
           <t>68933</t>
         </is>
@@ -8554,7 +8584,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U140" t="inlineStr">
+      <c r="X140" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -8612,7 +8642,7 @@
           <t>DELASSUS Marjorie</t>
         </is>
       </c>
-      <c r="U141" t="inlineStr">
+      <c r="X141" t="inlineStr">
         <is>
           <t>71964</t>
         </is>
@@ -8670,7 +8700,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U142" t="inlineStr">
+      <c r="X142" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -8834,7 +8864,7 @@
           <t>DANIELS Haley</t>
         </is>
       </c>
-      <c r="U145" t="inlineStr">
+      <c r="X145" t="inlineStr">
         <is>
           <t>36260</t>
         </is>
@@ -8892,7 +8922,7 @@
           <t>OHMAYER Birgit</t>
         </is>
       </c>
-      <c r="U146" t="inlineStr">
+      <c r="X146" t="inlineStr">
         <is>
           <t>39157</t>
         </is>
@@ -8950,7 +8980,7 @@
           <t>SKACHOVA Monika</t>
         </is>
       </c>
-      <c r="U147" t="inlineStr">
+      <c r="X147" t="inlineStr">
         <is>
           <t>53078</t>
         </is>
@@ -9008,7 +9038,7 @@
           <t>SABITOVA Zulfia</t>
         </is>
       </c>
-      <c r="U148" t="inlineStr">
+      <c r="X148" t="inlineStr">
         <is>
           <t>40572</t>
         </is>
@@ -9066,7 +9096,7 @@
           <t>GLEJTEKOVA Simona</t>
         </is>
       </c>
-      <c r="U149" t="inlineStr">
+      <c r="X149" t="inlineStr">
         <is>
           <t>55166</t>
         </is>
@@ -9124,7 +9154,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U150" t="inlineStr">
+      <c r="X150" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -9182,7 +9212,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U151" t="inlineStr">
+      <c r="X151" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -9240,7 +9270,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U152" t="inlineStr">
+      <c r="X152" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -9351,7 +9381,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U154" t="inlineStr">
+      <c r="X154" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -9409,7 +9439,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U155" t="inlineStr">
+      <c r="X155" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -9467,7 +9497,7 @@
           <t>VERMA Dharmendra</t>
         </is>
       </c>
-      <c r="U156" t="inlineStr">
+      <c r="X156" t="inlineStr">
         <is>
           <t>75387</t>
         </is>
@@ -9525,7 +9555,7 @@
           <t>KARLIVANS Toms</t>
         </is>
       </c>
-      <c r="U157" t="inlineStr">
+      <c r="X157" t="inlineStr">
         <is>
           <t>52325</t>
         </is>
@@ -9583,7 +9613,7 @@
           <t>CAPSTICK Finley</t>
         </is>
       </c>
-      <c r="U158" t="inlineStr">
+      <c r="X158" t="inlineStr">
         <is>
           <t>76710</t>
         </is>
@@ -9641,7 +9671,7 @@
           <t>KEER Kuldeep Singh</t>
         </is>
       </c>
-      <c r="U159" t="inlineStr">
+      <c r="X159" t="inlineStr">
         <is>
           <t>68932</t>
         </is>
@@ -9699,7 +9729,7 @@
           <t>KEER Dheeraj</t>
         </is>
       </c>
-      <c r="U160" t="inlineStr">
+      <c r="X160" t="inlineStr">
         <is>
           <t>68963</t>
         </is>
@@ -9757,7 +9787,7 @@
           <t>MCCREERY Alistair</t>
         </is>
       </c>
-      <c r="U161" t="inlineStr">
+      <c r="X161" t="inlineStr">
         <is>
           <t>60125</t>
         </is>
@@ -9815,7 +9845,7 @@
           <t>PRIGENT Yves</t>
         </is>
       </c>
-      <c r="U162" t="inlineStr">
+      <c r="X162" t="inlineStr">
         <is>
           <t>35671</t>
         </is>
@@ -9873,7 +9903,7 @@
           <t>RAMRATTAN Darius</t>
         </is>
       </c>
-      <c r="U163" t="inlineStr">
+      <c r="X163" t="inlineStr">
         <is>
           <t>60059</t>
         </is>
@@ -9931,7 +9961,7 @@
           <t>THOMPSON Angus</t>
         </is>
       </c>
-      <c r="U164" t="inlineStr">
+      <c r="X164" t="inlineStr">
         <is>
           <t>44814</t>
         </is>
@@ -9989,7 +10019,7 @@
           <t>KRIESINGER Ingo</t>
         </is>
       </c>
-      <c r="U165" t="inlineStr">
+      <c r="X165" t="inlineStr">
         <is>
           <t>35336</t>
         </is>
@@ -10047,7 +10077,7 @@
           <t>FARRELL Oisin</t>
         </is>
       </c>
-      <c r="U166" t="inlineStr">
+      <c r="X166" t="inlineStr">
         <is>
           <t>37916</t>
         </is>
@@ -10105,7 +10135,7 @@
           <t>SIMPSON Keenan</t>
         </is>
       </c>
-      <c r="U167" t="inlineStr">
+      <c r="X167" t="inlineStr">
         <is>
           <t>71797</t>
         </is>
@@ -10163,7 +10193,7 @@
           <t>HAWTHORNE Alex</t>
         </is>
       </c>
-      <c r="U168" t="inlineStr">
+      <c r="X168" t="inlineStr">
         <is>
           <t>51645</t>
         </is>
@@ -10221,7 +10251,7 @@
           <t>HENDRICK Noel</t>
         </is>
       </c>
-      <c r="U169" t="inlineStr">
+      <c r="X169" t="inlineStr">
         <is>
           <t>43003</t>
         </is>
@@ -10279,7 +10309,7 @@
           <t>SOARES Renan</t>
         </is>
       </c>
-      <c r="U170" t="inlineStr">
+      <c r="X170" t="inlineStr">
         <is>
           <t>42776</t>
         </is>
@@ -10337,7 +10367,7 @@
           <t>SAEKI Yutaro</t>
         </is>
       </c>
-      <c r="U171" t="inlineStr">
+      <c r="X171" t="inlineStr">
         <is>
           <t>37678</t>
         </is>
@@ -10395,7 +10425,7 @@
           <t>WESTFALL Tyler</t>
         </is>
       </c>
-      <c r="U172" t="inlineStr">
+      <c r="X172" t="inlineStr">
         <is>
           <t>51919</t>
         </is>
@@ -10453,7 +10483,7 @@
           <t>CORTEZ Geronimo</t>
         </is>
       </c>
-      <c r="U173" t="inlineStr">
+      <c r="X173" t="inlineStr">
         <is>
           <t>51835</t>
         </is>
@@ -10511,7 +10541,7 @@
           <t>YOSHIDA Taku</t>
         </is>
       </c>
-      <c r="U174" t="inlineStr">
+      <c r="X174" t="inlineStr">
         <is>
           <t>41611</t>
         </is>
@@ -10569,7 +10599,7 @@
           <t>ROSSI Lucas</t>
         </is>
       </c>
-      <c r="U175" t="inlineStr">
+      <c r="X175" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
@@ -10627,7 +10657,7 @@
           <t>JAKSE Zan</t>
         </is>
       </c>
-      <c r="U176" t="inlineStr">
+      <c r="X176" t="inlineStr">
         <is>
           <t>44340</t>
         </is>
@@ -10685,7 +10715,7 @@
           <t>POPE Benjamin</t>
         </is>
       </c>
-      <c r="U177" t="inlineStr">
+      <c r="X177" t="inlineStr">
         <is>
           <t>51753</t>
         </is>
@@ -10743,7 +10773,7 @@
           <t>MUNSCH Manuel</t>
         </is>
       </c>
-      <c r="U178" t="inlineStr">
+      <c r="X178" t="inlineStr">
         <is>
           <t>35631</t>
         </is>
@@ -10801,7 +10831,7 @@
           <t>MAPELLI Guilherme Marcello</t>
         </is>
       </c>
-      <c r="U179" t="inlineStr">
+      <c r="X179" t="inlineStr">
         <is>
           <t>38015</t>
         </is>
@@ -10859,7 +10889,7 @@
           <t>WAHLEN Fredrik</t>
         </is>
       </c>
-      <c r="U180" t="inlineStr">
+      <c r="X180" t="inlineStr">
         <is>
           <t>35102</t>
         </is>
@@ -10917,7 +10947,7 @@
           <t>WEGER Matthias</t>
         </is>
       </c>
-      <c r="U181" t="inlineStr">
+      <c r="X181" t="inlineStr">
         <is>
           <t>68837</t>
         </is>
@@ -10975,7 +11005,7 @@
           <t>POWELL Richard</t>
         </is>
       </c>
-      <c r="U182" t="inlineStr">
+      <c r="X182" t="inlineStr">
         <is>
           <t>36444</t>
         </is>
@@ -11033,7 +11063,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U183" t="inlineStr">
+      <c r="X183" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -11091,7 +11121,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U184" t="inlineStr">
+      <c r="X184" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -11149,7 +11179,7 @@
           <t>ADACHI Kazuya</t>
         </is>
       </c>
-      <c r="U185" t="inlineStr">
+      <c r="X185" t="inlineStr">
         <is>
           <t>36646</t>
         </is>
@@ -11207,7 +11237,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U186" t="inlineStr">
+      <c r="X186" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -11265,7 +11295,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U187" t="inlineStr">
+      <c r="X187" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -11323,7 +11353,7 @@
           <t>BRUS Simon</t>
         </is>
       </c>
-      <c r="U188" t="inlineStr">
+      <c r="X188" t="inlineStr">
         <is>
           <t>39076</t>
         </is>
@@ -11381,7 +11411,7 @@
           <t>MALEK Andrej</t>
         </is>
       </c>
-      <c r="U189" t="inlineStr">
+      <c r="X189" t="inlineStr">
         <is>
           <t>39246</t>
         </is>
@@ -11492,7 +11522,7 @@
           <t>LAUNAY Antoine</t>
         </is>
       </c>
-      <c r="U191" t="inlineStr">
+      <c r="X191" t="inlineStr">
         <is>
           <t>68776</t>
         </is>
@@ -11550,7 +11580,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U192" t="inlineStr">
+      <c r="X192" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -11608,7 +11638,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U193" t="inlineStr">
+      <c r="X193" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -11666,7 +11696,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U194" t="inlineStr">
+      <c r="X194" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -11724,7 +11754,7 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U195" t="inlineStr">
+      <c r="X195" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -11782,7 +11812,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U196" t="inlineStr">
+      <c r="X196" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -11840,7 +11870,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U197" t="inlineStr">
+      <c r="X197" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -12110,7 +12140,7 @@
           <t>MINTALOVA Eliska</t>
         </is>
       </c>
-      <c r="U202" t="inlineStr">
+      <c r="X202" t="inlineStr">
         <is>
           <t>56169</t>
         </is>
@@ -12168,7 +12198,7 @@
           <t>DHURWE Ganeshvri</t>
         </is>
       </c>
-      <c r="U203" t="inlineStr">
+      <c r="X203" t="inlineStr">
         <is>
           <t>68934</t>
         </is>
@@ -12226,7 +12256,7 @@
           <t>PANDEY Aarti</t>
         </is>
       </c>
-      <c r="U204" t="inlineStr">
+      <c r="X204" t="inlineStr">
         <is>
           <t>68936</t>
         </is>
@@ -12284,7 +12314,7 @@
           <t>LUCATO Eleonora</t>
         </is>
       </c>
-      <c r="U205" t="inlineStr">
+      <c r="X205" t="inlineStr">
         <is>
           <t>35222</t>
         </is>
@@ -12342,7 +12372,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U206" t="inlineStr">
+      <c r="X206" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -12400,7 +12430,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U207" t="inlineStr">
+      <c r="X207" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -12458,7 +12488,7 @@
           <t>ITO Yoshika</t>
         </is>
       </c>
-      <c r="U208" t="inlineStr">
+      <c r="X208" t="inlineStr">
         <is>
           <t>36647</t>
         </is>
@@ -12516,7 +12546,7 @@
           <t>OTTEN Maartje</t>
         </is>
       </c>
-      <c r="U209" t="inlineStr">
+      <c r="X209" t="inlineStr">
         <is>
           <t>35337</t>
         </is>
@@ -12574,7 +12604,7 @@
           <t>WILLIAMS Courtney</t>
         </is>
       </c>
-      <c r="U210" t="inlineStr">
+      <c r="X210" t="inlineStr">
         <is>
           <t>68771</t>
         </is>
@@ -12632,7 +12662,7 @@
           <t>GRATWOHL Andrea</t>
         </is>
       </c>
-      <c r="U211" t="inlineStr">
+      <c r="X211" t="inlineStr">
         <is>
           <t>35429</t>
         </is>
@@ -12690,7 +12720,7 @@
           <t>MAHEU Florence</t>
         </is>
       </c>
-      <c r="U212" t="inlineStr">
+      <c r="X212" t="inlineStr">
         <is>
           <t>36416</t>
         </is>
@@ -12801,7 +12831,7 @@
           <t>OSCHMAUTZ Antonia</t>
         </is>
       </c>
-      <c r="U214" t="inlineStr">
+      <c r="X214" t="inlineStr">
         <is>
           <t>68839</t>
         </is>
@@ -12859,7 +12889,7 @@
           <t>IFARRAGUERRI Anna Maria</t>
         </is>
       </c>
-      <c r="U215" t="inlineStr">
+      <c r="X215" t="inlineStr">
         <is>
           <t>39209</t>
         </is>
@@ -12917,7 +12947,7 @@
           <t>REN Ye</t>
         </is>
       </c>
-      <c r="U216" t="inlineStr">
+      <c r="X216" t="inlineStr">
         <is>
           <t>68810</t>
         </is>
@@ -12975,7 +13005,7 @@
           <t>WERATSCHNIG Nina</t>
         </is>
       </c>
-      <c r="U217" t="inlineStr">
+      <c r="X217" t="inlineStr">
         <is>
           <t>41614</t>
         </is>
@@ -13033,7 +13063,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U218" t="inlineStr">
+      <c r="X218" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -13091,7 +13121,7 @@
           <t>MEDON Joanna</t>
         </is>
       </c>
-      <c r="U219" t="inlineStr">
+      <c r="X219" t="inlineStr">
         <is>
           <t>35438</t>
         </is>
@@ -13149,7 +13179,7 @@
           <t>TAKESHITA Yuriko</t>
         </is>
       </c>
-      <c r="U220" t="inlineStr">
+      <c r="X220" t="inlineStr">
         <is>
           <t>36487</t>
         </is>
@@ -13207,7 +13237,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U221" t="inlineStr">
+      <c r="X221" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -13265,7 +13295,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U222" t="inlineStr">
+      <c r="X222" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -13323,7 +13353,7 @@
           <t>HILGERTOVA Amalie</t>
         </is>
       </c>
-      <c r="U223" t="inlineStr">
+      <c r="X223" t="inlineStr">
         <is>
           <t>36113</t>
         </is>
@@ -13381,7 +13411,7 @@
           <t>TROMPETER Caroline</t>
         </is>
       </c>
-      <c r="U224" t="inlineStr">
+      <c r="X224" t="inlineStr">
         <is>
           <t>39167</t>
         </is>
@@ -13439,7 +13469,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U225" t="inlineStr">
+      <c r="X225" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -13497,7 +13527,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U226" t="inlineStr">
+      <c r="X226" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -13555,7 +13585,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U227" t="inlineStr">
+      <c r="X227" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -13613,7 +13643,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U228" t="inlineStr">
+      <c r="X228" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -13671,7 +13701,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U229" t="inlineStr">
+      <c r="X229" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -13729,7 +13759,7 @@
           <t>PEROVA Aleksandra</t>
         </is>
       </c>
-      <c r="U230" t="inlineStr">
+      <c r="X230" t="inlineStr">
         <is>
           <t>35256</t>
         </is>
@@ -13787,7 +13817,7 @@
           <t>GOIKOETXEA Irati</t>
         </is>
       </c>
-      <c r="U231" t="inlineStr">
+      <c r="X231" t="inlineStr">
         <is>
           <t>35761</t>
         </is>
@@ -13845,7 +13875,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U232" t="inlineStr">
+      <c r="X232" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -13903,7 +13933,7 @@
           <t>KALISKA Elena</t>
         </is>
       </c>
-      <c r="U233" t="inlineStr">
+      <c r="X233" t="inlineStr">
         <is>
           <t>35366</t>
         </is>
@@ -13961,7 +13991,7 @@
           <t>PEROVA Ekaterina</t>
         </is>
       </c>
-      <c r="U234" t="inlineStr">
+      <c r="X234" t="inlineStr">
         <is>
           <t>35131</t>
         </is>
@@ -14019,7 +14049,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U235" t="inlineStr">
+      <c r="X235" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -14077,7 +14107,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U236" t="inlineStr">
+      <c r="X236" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -14135,7 +14165,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U237" t="inlineStr">
+      <c r="X237" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -14193,7 +14223,7 @@
           <t>GALUSKOVA Karolina</t>
         </is>
       </c>
-      <c r="U238" t="inlineStr">
+      <c r="X238" t="inlineStr">
         <is>
           <t>37266</t>
         </is>
@@ -14251,7 +14281,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U239" t="inlineStr">
+      <c r="X239" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -14309,7 +14339,7 @@
           <t>PENNIE Fiona</t>
         </is>
       </c>
-      <c r="U240" t="inlineStr">
+      <c r="X240" t="inlineStr">
         <is>
           <t>35638</t>
         </is>
@@ -14367,7 +14397,7 @@
           <t>HILGERTOVA Stepanka</t>
         </is>
       </c>
-      <c r="U241" t="inlineStr">
+      <c r="X241" t="inlineStr">
         <is>
           <t>35035</t>
         </is>
@@ -14425,7 +14455,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U242" t="inlineStr">
+      <c r="X242" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -14483,7 +14513,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U243" t="inlineStr">
+      <c r="X243" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -14541,7 +14571,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U244" t="inlineStr">
+      <c r="X244" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -14599,7 +14629,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U245" t="inlineStr">
+      <c r="X245" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -14657,7 +14687,7 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U246" t="inlineStr">
+      <c r="X246" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -14715,7 +14745,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U247" t="inlineStr">
+      <c r="X247" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -14773,7 +14803,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U248" t="inlineStr">
+      <c r="X248" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -14831,7 +14861,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U249" t="inlineStr">
+      <c r="X249" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -14889,7 +14919,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U250" t="inlineStr">
+      <c r="X250" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -14947,7 +14977,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U251" t="inlineStr">
+      <c r="X251" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -15005,7 +15035,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U252" t="inlineStr">
+      <c r="X252" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -15063,7 +15093,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U253" t="inlineStr">
+      <c r="X253" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -15121,7 +15151,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U254" t="inlineStr">
+      <c r="X254" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -15179,7 +15209,7 @@
           <t>KUSHWAHA Vishvjeet</t>
         </is>
       </c>
-      <c r="U255" t="inlineStr">
+      <c r="X255" t="inlineStr">
         <is>
           <t>68966</t>
         </is>
@@ -15237,7 +15267,7 @@
           <t>SZCZEPANSKI Piotr</t>
         </is>
       </c>
-      <c r="U256" t="inlineStr">
+      <c r="X256" t="inlineStr">
         <is>
           <t>35080</t>
         </is>
@@ -15295,7 +15325,7 @@
           <t>BATHAM Virendra</t>
         </is>
       </c>
-      <c r="U257" t="inlineStr">
+      <c r="X257" t="inlineStr">
         <is>
           <t>68965</t>
         </is>
@@ -15353,7 +15383,7 @@
           <t>PARMAR Prince</t>
         </is>
       </c>
-      <c r="U258" t="inlineStr">
+      <c r="X258" t="inlineStr">
         <is>
           <t>68938</t>
         </is>
@@ -15411,7 +15441,7 @@
           <t>OTTEN Joris</t>
         </is>
       </c>
-      <c r="U259" t="inlineStr">
+      <c r="X259" t="inlineStr">
         <is>
           <t>41698</t>
         </is>
@@ -15469,7 +15499,7 @@
           <t>REN Qinkang</t>
         </is>
       </c>
-      <c r="U260" t="inlineStr">
+      <c r="X260" t="inlineStr">
         <is>
           <t>75438</t>
         </is>
@@ -15527,7 +15557,7 @@
           <t>McEWAN Devin</t>
         </is>
       </c>
-      <c r="U261" t="inlineStr">
+      <c r="X261" t="inlineStr">
         <is>
           <t>35068</t>
         </is>
@@ -15585,7 +15615,7 @@
           <t>LE RUYET Edern</t>
         </is>
       </c>
-      <c r="U262" t="inlineStr">
+      <c r="X262" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
@@ -15643,7 +15673,7 @@
           <t>MARC Jonathan</t>
         </is>
       </c>
-      <c r="U263" t="inlineStr">
+      <c r="X263" t="inlineStr">
         <is>
           <t>35388</t>
         </is>
@@ -15701,7 +15731,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U264" t="inlineStr">
+      <c r="X264" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -15759,7 +15789,7 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U265" t="inlineStr">
+      <c r="X265" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -15817,7 +15847,7 @@
           <t>SASAKI Shota</t>
         </is>
       </c>
-      <c r="U266" t="inlineStr">
+      <c r="X266" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -15875,7 +15905,7 @@
           <t>LHOTA Matyas</t>
         </is>
       </c>
-      <c r="U267" t="inlineStr">
+      <c r="X267" t="inlineStr">
         <is>
           <t>51872</t>
         </is>
@@ -15933,7 +15963,7 @@
           <t>POMEROY Spencer</t>
         </is>
       </c>
-      <c r="U268" t="inlineStr">
+      <c r="X268" t="inlineStr">
         <is>
           <t>57783</t>
         </is>
@@ -15991,7 +16021,7 @@
           <t>WASHER Patrick</t>
         </is>
       </c>
-      <c r="U269" t="inlineStr">
+      <c r="X269" t="inlineStr">
         <is>
           <t>42081</t>
         </is>
@@ -16049,7 +16079,7 @@
           <t>FERNANDEZ Luis</t>
         </is>
       </c>
-      <c r="U270" t="inlineStr">
+      <c r="X270" t="inlineStr">
         <is>
           <t>51851</t>
         </is>
@@ -16107,7 +16137,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U271" t="inlineStr">
+      <c r="X271" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -16165,7 +16195,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U272" t="inlineStr">
+      <c r="X272" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -16223,7 +16253,7 @@
           <t>CORREA Charles</t>
         </is>
       </c>
-      <c r="U273" t="inlineStr">
+      <c r="X273" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
@@ -16281,7 +16311,7 @@
           <t>CARTER Tristan</t>
         </is>
       </c>
-      <c r="U274" t="inlineStr">
+      <c r="X274" t="inlineStr">
         <is>
           <t>51890</t>
         </is>
@@ -16339,7 +16369,7 @@
           <t>CURCEL Leonardo</t>
         </is>
       </c>
-      <c r="U275" t="inlineStr">
+      <c r="X275" t="inlineStr">
         <is>
           <t>38014</t>
         </is>
@@ -16397,7 +16427,7 @@
           <t>SZTUBA Kacper</t>
         </is>
       </c>
-      <c r="U276" t="inlineStr">
+      <c r="X276" t="inlineStr">
         <is>
           <t>53636</t>
         </is>
@@ -16455,7 +16485,7 @@
           <t>CHALOUPKA Vaclav</t>
         </is>
       </c>
-      <c r="U277" t="inlineStr">
+      <c r="X277" t="inlineStr">
         <is>
           <t>51648</t>
         </is>
@@ -16513,7 +16543,7 @@
           <t>BORGES Felipe</t>
         </is>
       </c>
-      <c r="U278" t="inlineStr">
+      <c r="X278" t="inlineStr">
         <is>
           <t>38012</t>
         </is>
@@ -16571,7 +16601,7 @@
           <t>ROSSI Sebastian</t>
         </is>
       </c>
-      <c r="U279" t="inlineStr">
+      <c r="X279" t="inlineStr">
         <is>
           <t>36915</t>
         </is>
@@ -16629,7 +16659,7 @@
           <t>SETKIN Kirill</t>
         </is>
       </c>
-      <c r="U280" t="inlineStr">
+      <c r="X280" t="inlineStr">
         <is>
           <t>35457</t>
         </is>
@@ -16687,7 +16717,7 @@
           <t>BORROWS Ian</t>
         </is>
       </c>
-      <c r="U281" t="inlineStr">
+      <c r="X281" t="inlineStr">
         <is>
           <t>36534</t>
         </is>
@@ -16745,7 +16775,7 @@
           <t>IVALDI Raffaello</t>
         </is>
       </c>
-      <c r="U282" t="inlineStr">
+      <c r="X282" t="inlineStr">
         <is>
           <t>35227</t>
         </is>
@@ -16803,7 +16833,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U283" t="inlineStr">
+      <c r="X283" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -16861,7 +16891,7 @@
           <t>CIPRESSI Stefano</t>
         </is>
       </c>
-      <c r="U284" t="inlineStr">
+      <c r="X284" t="inlineStr">
         <is>
           <t>35495</t>
         </is>
@@ -16919,7 +16949,7 @@
           <t>BADURA Jergus</t>
         </is>
       </c>
-      <c r="U285" t="inlineStr">
+      <c r="X285" t="inlineStr">
         <is>
           <t>68767</t>
         </is>
@@ -16977,7 +17007,7 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U286" t="inlineStr">
+      <c r="X286" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -17035,7 +17065,7 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U287" t="inlineStr">
+      <c r="X287" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -17093,7 +17123,7 @@
           <t>COLAZINGARI Roberto</t>
         </is>
       </c>
-      <c r="U288" t="inlineStr">
+      <c r="X288" t="inlineStr">
         <is>
           <t>35223</t>
         </is>
@@ -17151,7 +17181,7 @@
           <t>JANE Michal</t>
         </is>
       </c>
-      <c r="U289" t="inlineStr">
+      <c r="X289" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
@@ -17209,7 +17239,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U290" t="inlineStr">
+      <c r="X290" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -17267,7 +17297,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U291" t="inlineStr">
+      <c r="X291" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -17325,7 +17355,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U292" t="inlineStr">
+      <c r="X292" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -17383,7 +17413,7 @@
           <t>ELOSEGI Ander</t>
         </is>
       </c>
-      <c r="U293" t="inlineStr">
+      <c r="X293" t="inlineStr">
         <is>
           <t>35785</t>
         </is>
@@ -17441,7 +17471,7 @@
           <t>ROHAN Lukas</t>
         </is>
       </c>
-      <c r="U294" t="inlineStr">
+      <c r="X294" t="inlineStr">
         <is>
           <t>36114</t>
         </is>
@@ -17499,7 +17529,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U295" t="inlineStr">
+      <c r="X295" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -17557,7 +17587,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U296" t="inlineStr">
+      <c r="X296" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -17615,7 +17645,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U297" t="inlineStr">
+      <c r="X297" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -17673,7 +17703,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U298" t="inlineStr">
+      <c r="X298" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -17731,7 +17761,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U299" t="inlineStr">
+      <c r="X299" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -17789,7 +17819,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U300" t="inlineStr">
+      <c r="X300" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -17847,7 +17877,7 @@
           <t>HANEDA Takuya</t>
         </is>
       </c>
-      <c r="U301" t="inlineStr">
+      <c r="X301" t="inlineStr">
         <is>
           <t>36481</t>
         </is>
@@ -17905,7 +17935,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U302" t="inlineStr">
+      <c r="X302" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -17963,7 +17993,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U303" t="inlineStr">
+      <c r="X303" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
@@ -18021,7 +18051,7 @@
           <t>FLORENCE David</t>
         </is>
       </c>
-      <c r="U304" t="inlineStr">
+      <c r="X304" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -18079,7 +18109,7 @@
           <t>GARGAUD CHANUT Denis</t>
         </is>
       </c>
-      <c r="U305" t="inlineStr">
+      <c r="X305" t="inlineStr">
         <is>
           <t>35177</t>
         </is>
@@ -18137,7 +18167,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U306" t="inlineStr">
+      <c r="X306" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -18195,7 +18225,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U307" t="inlineStr">
+      <c r="X307" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -18253,7 +18283,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U308" t="inlineStr">
+      <c r="X308" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -18311,7 +18341,7 @@
           <t>MINTALOVA Eliska</t>
         </is>
       </c>
-      <c r="U309" t="inlineStr">
+      <c r="X309" t="inlineStr">
         <is>
           <t>56169</t>
         </is>
@@ -18369,7 +18399,7 @@
           <t>DHURWE Ganeshvri</t>
         </is>
       </c>
-      <c r="U310" t="inlineStr">
+      <c r="X310" t="inlineStr">
         <is>
           <t>68934</t>
         </is>
@@ -18427,7 +18457,7 @@
           <t>PANDEY Aarti</t>
         </is>
       </c>
-      <c r="U311" t="inlineStr">
+      <c r="X311" t="inlineStr">
         <is>
           <t>68936</t>
         </is>
@@ -18485,7 +18515,7 @@
           <t>LUCATO Eleonora</t>
         </is>
       </c>
-      <c r="U312" t="inlineStr">
+      <c r="X312" t="inlineStr">
         <is>
           <t>35222</t>
         </is>
@@ -18543,7 +18573,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U313" t="inlineStr">
+      <c r="X313" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -18601,7 +18631,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U314" t="inlineStr">
+      <c r="X314" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -18659,7 +18689,7 @@
           <t>ITO Yoshika</t>
         </is>
       </c>
-      <c r="U315" t="inlineStr">
+      <c r="X315" t="inlineStr">
         <is>
           <t>36647</t>
         </is>
@@ -18717,7 +18747,7 @@
           <t>OTTEN Maartje</t>
         </is>
       </c>
-      <c r="U316" t="inlineStr">
+      <c r="X316" t="inlineStr">
         <is>
           <t>35337</t>
         </is>
@@ -18775,7 +18805,7 @@
           <t>WILLIAMS Courtney</t>
         </is>
       </c>
-      <c r="U317" t="inlineStr">
+      <c r="X317" t="inlineStr">
         <is>
           <t>68771</t>
         </is>
@@ -18833,7 +18863,7 @@
           <t>GRATWOHL Andrea</t>
         </is>
       </c>
-      <c r="U318" t="inlineStr">
+      <c r="X318" t="inlineStr">
         <is>
           <t>35429</t>
         </is>
@@ -18891,7 +18921,7 @@
           <t>MAHEU Florence</t>
         </is>
       </c>
-      <c r="U319" t="inlineStr">
+      <c r="X319" t="inlineStr">
         <is>
           <t>36416</t>
         </is>
@@ -19002,7 +19032,7 @@
           <t>OSCHMAUTZ Antonia</t>
         </is>
       </c>
-      <c r="U321" t="inlineStr">
+      <c r="X321" t="inlineStr">
         <is>
           <t>68839</t>
         </is>
@@ -19060,7 +19090,7 @@
           <t>IFARRAGUERRI Anna Maria</t>
         </is>
       </c>
-      <c r="U322" t="inlineStr">
+      <c r="X322" t="inlineStr">
         <is>
           <t>39209</t>
         </is>
@@ -19118,7 +19148,7 @@
           <t>REN Ye</t>
         </is>
       </c>
-      <c r="U323" t="inlineStr">
+      <c r="X323" t="inlineStr">
         <is>
           <t>68810</t>
         </is>
@@ -19176,7 +19206,7 @@
           <t>WERATSCHNIG Nina</t>
         </is>
       </c>
-      <c r="U324" t="inlineStr">
+      <c r="X324" t="inlineStr">
         <is>
           <t>41614</t>
         </is>
@@ -19234,7 +19264,7 @@
           <t>PRIGENT Camille</t>
         </is>
       </c>
-      <c r="U325" t="inlineStr">
+      <c r="X325" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
@@ -19292,7 +19322,7 @@
           <t>MEDON Joanna</t>
         </is>
       </c>
-      <c r="U326" t="inlineStr">
+      <c r="X326" t="inlineStr">
         <is>
           <t>35438</t>
         </is>
@@ -19350,7 +19380,7 @@
           <t>TAKESHITA Yuriko</t>
         </is>
       </c>
-      <c r="U327" t="inlineStr">
+      <c r="X327" t="inlineStr">
         <is>
           <t>36487</t>
         </is>
@@ -19408,7 +19438,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U328" t="inlineStr">
+      <c r="X328" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -19466,7 +19496,7 @@
           <t>HILGERTOVA Amalie</t>
         </is>
       </c>
-      <c r="U329" t="inlineStr">
+      <c r="X329" t="inlineStr">
         <is>
           <t>36113</t>
         </is>
@@ -19524,7 +19554,7 @@
           <t>TROMPETER Caroline</t>
         </is>
       </c>
-      <c r="U330" t="inlineStr">
+      <c r="X330" t="inlineStr">
         <is>
           <t>39167</t>
         </is>
@@ -19582,7 +19612,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U331" t="inlineStr">
+      <c r="X331" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -19640,7 +19670,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U332" t="inlineStr">
+      <c r="X332" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -19698,7 +19728,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U333" t="inlineStr">
+      <c r="X333" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -19756,7 +19786,7 @@
           <t>PEROVA Aleksandra</t>
         </is>
       </c>
-      <c r="U334" t="inlineStr">
+      <c r="X334" t="inlineStr">
         <is>
           <t>35256</t>
         </is>
@@ -19814,7 +19844,7 @@
           <t>GOIKOETXEA Irati</t>
         </is>
       </c>
-      <c r="U335" t="inlineStr">
+      <c r="X335" t="inlineStr">
         <is>
           <t>35761</t>
         </is>
@@ -19872,7 +19902,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U336" t="inlineStr">
+      <c r="X336" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -19930,7 +19960,7 @@
           <t>KALISKA Elena</t>
         </is>
       </c>
-      <c r="U337" t="inlineStr">
+      <c r="X337" t="inlineStr">
         <is>
           <t>35366</t>
         </is>
@@ -19988,7 +20018,7 @@
           <t>PEROVA Ekaterina</t>
         </is>
       </c>
-      <c r="U338" t="inlineStr">
+      <c r="X338" t="inlineStr">
         <is>
           <t>35131</t>
         </is>
@@ -20046,7 +20076,7 @@
           <t>GALUSKOVA Karolina</t>
         </is>
       </c>
-      <c r="U339" t="inlineStr">
+      <c r="X339" t="inlineStr">
         <is>
           <t>37266</t>
         </is>
@@ -20104,7 +20134,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U340" t="inlineStr">
+      <c r="X340" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -20162,7 +20192,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U341" t="inlineStr">
+      <c r="X341" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -20220,7 +20250,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U342" t="inlineStr">
+      <c r="X342" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -20278,7 +20308,7 @@
           <t>KUSHWAHA Vishvjeet</t>
         </is>
       </c>
-      <c r="U343" t="inlineStr">
+      <c r="X343" t="inlineStr">
         <is>
           <t>68966</t>
         </is>
@@ -20336,7 +20366,7 @@
           <t>SZCZEPANSKI Piotr</t>
         </is>
       </c>
-      <c r="U344" t="inlineStr">
+      <c r="X344" t="inlineStr">
         <is>
           <t>35080</t>
         </is>
@@ -20394,7 +20424,7 @@
           <t>BATHAM Virendra</t>
         </is>
       </c>
-      <c r="U345" t="inlineStr">
+      <c r="X345" t="inlineStr">
         <is>
           <t>68965</t>
         </is>
@@ -20452,7 +20482,7 @@
           <t>PARMAR Prince</t>
         </is>
       </c>
-      <c r="U346" t="inlineStr">
+      <c r="X346" t="inlineStr">
         <is>
           <t>68938</t>
         </is>
@@ -20510,7 +20540,7 @@
           <t>OTTEN Joris</t>
         </is>
       </c>
-      <c r="U347" t="inlineStr">
+      <c r="X347" t="inlineStr">
         <is>
           <t>41698</t>
         </is>
@@ -20568,7 +20598,7 @@
           <t>REN Qinkang</t>
         </is>
       </c>
-      <c r="U348" t="inlineStr">
+      <c r="X348" t="inlineStr">
         <is>
           <t>75438</t>
         </is>
@@ -20626,7 +20656,7 @@
           <t>McEWAN Devin</t>
         </is>
       </c>
-      <c r="U349" t="inlineStr">
+      <c r="X349" t="inlineStr">
         <is>
           <t>35068</t>
         </is>
@@ -20684,7 +20714,7 @@
           <t>LE RUYET Edern</t>
         </is>
       </c>
-      <c r="U350" t="inlineStr">
+      <c r="X350" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
@@ -20742,7 +20772,7 @@
           <t>MARC Jonathan</t>
         </is>
       </c>
-      <c r="U351" t="inlineStr">
+      <c r="X351" t="inlineStr">
         <is>
           <t>35388</t>
         </is>
@@ -20800,7 +20830,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U352" t="inlineStr">
+      <c r="X352" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -20858,7 +20888,7 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U353" t="inlineStr">
+      <c r="X353" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -20916,7 +20946,7 @@
           <t>SASAKI Shota</t>
         </is>
       </c>
-      <c r="U354" t="inlineStr">
+      <c r="X354" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -20974,7 +21004,7 @@
           <t>LHOTA Matyas</t>
         </is>
       </c>
-      <c r="U355" t="inlineStr">
+      <c r="X355" t="inlineStr">
         <is>
           <t>51872</t>
         </is>
@@ -21032,7 +21062,7 @@
           <t>POMEROY Spencer</t>
         </is>
       </c>
-      <c r="U356" t="inlineStr">
+      <c r="X356" t="inlineStr">
         <is>
           <t>57783</t>
         </is>
@@ -21090,7 +21120,7 @@
           <t>WASHER Patrick</t>
         </is>
       </c>
-      <c r="U357" t="inlineStr">
+      <c r="X357" t="inlineStr">
         <is>
           <t>42081</t>
         </is>
@@ -21148,7 +21178,7 @@
           <t>FERNANDEZ Luis</t>
         </is>
       </c>
-      <c r="U358" t="inlineStr">
+      <c r="X358" t="inlineStr">
         <is>
           <t>51851</t>
         </is>
@@ -21206,7 +21236,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U359" t="inlineStr">
+      <c r="X359" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -21264,7 +21294,7 @@
           <t>CORREA Charles</t>
         </is>
       </c>
-      <c r="U360" t="inlineStr">
+      <c r="X360" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
@@ -21322,7 +21352,7 @@
           <t>CARTER Tristan</t>
         </is>
       </c>
-      <c r="U361" t="inlineStr">
+      <c r="X361" t="inlineStr">
         <is>
           <t>51890</t>
         </is>
@@ -21380,7 +21410,7 @@
           <t>CURCEL Leonardo</t>
         </is>
       </c>
-      <c r="U362" t="inlineStr">
+      <c r="X362" t="inlineStr">
         <is>
           <t>38014</t>
         </is>
@@ -21438,7 +21468,7 @@
           <t>SZTUBA Kacper</t>
         </is>
       </c>
-      <c r="U363" t="inlineStr">
+      <c r="X363" t="inlineStr">
         <is>
           <t>53636</t>
         </is>
@@ -21496,7 +21526,7 @@
           <t>CHALOUPKA Vaclav</t>
         </is>
       </c>
-      <c r="U364" t="inlineStr">
+      <c r="X364" t="inlineStr">
         <is>
           <t>51648</t>
         </is>
@@ -21554,7 +21584,7 @@
           <t>BORGES Felipe</t>
         </is>
       </c>
-      <c r="U365" t="inlineStr">
+      <c r="X365" t="inlineStr">
         <is>
           <t>38012</t>
         </is>
@@ -21612,7 +21642,7 @@
           <t>ROSSI Sebastian</t>
         </is>
       </c>
-      <c r="U366" t="inlineStr">
+      <c r="X366" t="inlineStr">
         <is>
           <t>36915</t>
         </is>
@@ -21670,7 +21700,7 @@
           <t>SETKIN Kirill</t>
         </is>
       </c>
-      <c r="U367" t="inlineStr">
+      <c r="X367" t="inlineStr">
         <is>
           <t>35457</t>
         </is>
@@ -21728,7 +21758,7 @@
           <t>BORROWS Ian</t>
         </is>
       </c>
-      <c r="U368" t="inlineStr">
+      <c r="X368" t="inlineStr">
         <is>
           <t>36534</t>
         </is>
@@ -21786,7 +21816,7 @@
           <t>IVALDI Raffaello</t>
         </is>
       </c>
-      <c r="U369" t="inlineStr">
+      <c r="X369" t="inlineStr">
         <is>
           <t>35227</t>
         </is>
@@ -21844,7 +21874,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U370" t="inlineStr">
+      <c r="X370" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -21902,7 +21932,7 @@
           <t>CIPRESSI Stefano</t>
         </is>
       </c>
-      <c r="U371" t="inlineStr">
+      <c r="X371" t="inlineStr">
         <is>
           <t>35495</t>
         </is>
@@ -21960,7 +21990,7 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U372" t="inlineStr">
+      <c r="X372" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -22018,7 +22048,7 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U373" t="inlineStr">
+      <c r="X373" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -22076,7 +22106,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U374" t="inlineStr">
+      <c r="X374" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -22134,7 +22164,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U375" t="inlineStr">
+      <c r="X375" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -22192,7 +22222,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U376" t="inlineStr">
+      <c r="X376" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -22250,7 +22280,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U377" t="inlineStr">
+      <c r="X377" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -22573,12 +22603,12 @@
           <t>HEGER Vojtech</t>
         </is>
       </c>
-      <c r="U383" t="inlineStr">
+      <c r="X383" t="inlineStr">
         <is>
           <t>42007</t>
         </is>
       </c>
-      <c r="V383" t="inlineStr">
+      <c r="Y383" t="inlineStr">
         <is>
           <t>68872</t>
         </is>
@@ -22641,12 +22671,12 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U384" t="inlineStr">
+      <c r="X384" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
       </c>
-      <c r="V384" t="inlineStr">
+      <c r="Y384" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -22709,12 +22739,12 @@
           <t>CAILHOL Hugo</t>
         </is>
       </c>
-      <c r="U385" t="inlineStr">
+      <c r="X385" t="inlineStr">
         <is>
           <t>35476</t>
         </is>
       </c>
-      <c r="V385" t="inlineStr">
+      <c r="Y385" t="inlineStr">
         <is>
           <t>35491</t>
         </is>
@@ -22777,12 +22807,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U386" t="inlineStr">
+      <c r="X386" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V386" t="inlineStr">
+      <c r="Y386" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -22845,12 +22875,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U387" t="inlineStr">
+      <c r="X387" t="inlineStr">
         <is>
           <t>35368</t>
         </is>
       </c>
-      <c r="V387" t="inlineStr">
+      <c r="Y387" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -22913,12 +22943,12 @@
           <t>SKANTAR Peter</t>
         </is>
       </c>
-      <c r="U388" t="inlineStr">
+      <c r="X388" t="inlineStr">
         <is>
           <t>35360</t>
         </is>
       </c>
-      <c r="V388" t="inlineStr">
+      <c r="Y388" t="inlineStr">
         <is>
           <t>35361</t>
         </is>
@@ -22981,12 +23011,12 @@
           <t>BISO Hugo</t>
         </is>
       </c>
-      <c r="U389" t="inlineStr">
+      <c r="X389" t="inlineStr">
         <is>
           <t>35403</t>
         </is>
       </c>
-      <c r="V389" t="inlineStr">
+      <c r="Y389" t="inlineStr">
         <is>
           <t>35229</t>
         </is>
@@ -23049,12 +23079,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U390" t="inlineStr">
+      <c r="X390" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V390" t="inlineStr">
+      <c r="Y390" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -23117,12 +23147,12 @@
           <t>MUELLER Kevin</t>
         </is>
       </c>
-      <c r="U391" t="inlineStr">
+      <c r="X391" t="inlineStr">
         <is>
           <t>35148</t>
         </is>
       </c>
-      <c r="V391" t="inlineStr">
+      <c r="Y391" t="inlineStr">
         <is>
           <t>35149</t>
         </is>
@@ -23185,12 +23215,12 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U392" t="inlineStr">
+      <c r="X392" t="inlineStr">
         <is>
           <t>35145</t>
         </is>
       </c>
-      <c r="V392" t="inlineStr">
+      <c r="Y392" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -23253,12 +23283,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U393" t="inlineStr">
+      <c r="X393" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V393" t="inlineStr">
+      <c r="Y393" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -23321,12 +23351,12 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="U394" t="inlineStr">
+      <c r="X394" t="inlineStr">
         <is>
           <t>35060</t>
         </is>
       </c>
-      <c r="V394" t="inlineStr">
+      <c r="Y394" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -23389,12 +23419,12 @@
           <t>BENZIEN Jan</t>
         </is>
       </c>
-      <c r="U395" t="inlineStr">
+      <c r="X395" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
       </c>
-      <c r="V395" t="inlineStr">
+      <c r="Y395" t="inlineStr">
         <is>
           <t>35134</t>
         </is>
@@ -23452,7 +23482,7 @@
           <t>OHMAYER Birgit</t>
         </is>
       </c>
-      <c r="U396" t="inlineStr">
+      <c r="X396" t="inlineStr">
         <is>
           <t>39157</t>
         </is>
@@ -23510,7 +23540,7 @@
           <t>DANIELS Haley</t>
         </is>
       </c>
-      <c r="U397" t="inlineStr">
+      <c r="X397" t="inlineStr">
         <is>
           <t>36260</t>
         </is>
@@ -23568,7 +23598,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U398" t="inlineStr">
+      <c r="X398" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -23626,7 +23656,7 @@
           <t>GLEJTEKOVA Simona</t>
         </is>
       </c>
-      <c r="U399" t="inlineStr">
+      <c r="X399" t="inlineStr">
         <is>
           <t>55166</t>
         </is>
@@ -23737,7 +23767,7 @@
           <t>SABITOVA Zulfia</t>
         </is>
       </c>
-      <c r="U401" t="inlineStr">
+      <c r="X401" t="inlineStr">
         <is>
           <t>40572</t>
         </is>
@@ -23795,7 +23825,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U402" t="inlineStr">
+      <c r="X402" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -23853,7 +23883,7 @@
           <t>DELASSUS Marjorie</t>
         </is>
       </c>
-      <c r="U403" t="inlineStr">
+      <c r="X403" t="inlineStr">
         <is>
           <t>71964</t>
         </is>
@@ -23911,7 +23941,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U404" t="inlineStr">
+      <c r="X404" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -23969,7 +23999,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U405" t="inlineStr">
+      <c r="X405" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -24027,7 +24057,7 @@
           <t>TRETIAKOVA Svetlana</t>
         </is>
       </c>
-      <c r="U406" t="inlineStr">
+      <c r="X406" t="inlineStr">
         <is>
           <t>68775</t>
         </is>
@@ -24085,7 +24115,7 @@
           <t>MUKHGALEEVA Polina</t>
         </is>
       </c>
-      <c r="U407" t="inlineStr">
+      <c r="X407" t="inlineStr">
         <is>
           <t>35768</t>
         </is>
@@ -24143,7 +24173,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U408" t="inlineStr">
+      <c r="X408" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -24201,7 +24231,7 @@
           <t>HENRY Margaux</t>
         </is>
       </c>
-      <c r="U409" t="inlineStr">
+      <c r="X409" t="inlineStr">
         <is>
           <t>51995</t>
         </is>
@@ -24259,7 +24289,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U410" t="inlineStr">
+      <c r="X410" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -24317,7 +24347,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U411" t="inlineStr">
+      <c r="X411" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -24375,7 +24405,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U412" t="inlineStr">
+      <c r="X412" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -24433,7 +24463,7 @@
           <t>MACEKOVA Simona</t>
         </is>
       </c>
-      <c r="U413" t="inlineStr">
+      <c r="X413" t="inlineStr">
         <is>
           <t>45153</t>
         </is>
@@ -24491,7 +24521,7 @@
           <t>JANCOVA Monika</t>
         </is>
       </c>
-      <c r="U414" t="inlineStr">
+      <c r="X414" t="inlineStr">
         <is>
           <t>36015</t>
         </is>
@@ -24602,7 +24632,7 @@
           <t>RIHOVA Eva</t>
         </is>
       </c>
-      <c r="U416" t="inlineStr">
+      <c r="X416" t="inlineStr">
         <is>
           <t>51791</t>
         </is>
@@ -24660,7 +24690,7 @@
           <t>HERZOG Andrea</t>
         </is>
       </c>
-      <c r="U417" t="inlineStr">
+      <c r="X417" t="inlineStr">
         <is>
           <t>55099</t>
         </is>
@@ -24718,7 +24748,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U418" t="inlineStr">
+      <c r="X418" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -24776,7 +24806,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U419" t="inlineStr">
+      <c r="X419" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -24834,7 +24864,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U420" t="inlineStr">
+      <c r="X420" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -24892,7 +24922,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U421" t="inlineStr">
+      <c r="X421" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -25003,7 +25033,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U423" t="inlineStr">
+      <c r="X423" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -25061,7 +25091,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U424" t="inlineStr">
+      <c r="X424" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -25119,7 +25149,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U425" t="inlineStr">
+      <c r="X425" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -25177,7 +25207,7 @@
           <t>JAKSE Zan</t>
         </is>
       </c>
-      <c r="U426" t="inlineStr">
+      <c r="X426" t="inlineStr">
         <is>
           <t>44340</t>
         </is>
@@ -25235,7 +25265,7 @@
           <t>BRUS Simon</t>
         </is>
       </c>
-      <c r="U427" t="inlineStr">
+      <c r="X427" t="inlineStr">
         <is>
           <t>39076</t>
         </is>
@@ -25293,7 +25323,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U428" t="inlineStr">
+      <c r="X428" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -25351,7 +25381,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U429" t="inlineStr">
+      <c r="X429" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -25409,7 +25439,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U430" t="inlineStr">
+      <c r="X430" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -25467,7 +25497,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U431" t="inlineStr">
+      <c r="X431" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -25525,7 +25555,7 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U432" t="inlineStr">
+      <c r="X432" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -25583,7 +25613,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U433" t="inlineStr">
+      <c r="X433" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -25641,7 +25671,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U434" t="inlineStr">
+      <c r="X434" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -25699,7 +25729,7 @@
           <t>ADACHI Kazuya</t>
         </is>
       </c>
-      <c r="U435" t="inlineStr">
+      <c r="X435" t="inlineStr">
         <is>
           <t>36646</t>
         </is>
@@ -25757,7 +25787,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U436" t="inlineStr">
+      <c r="X436" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -25815,7 +25845,7 @@
           <t>BIAZIZZO Mathieu</t>
         </is>
       </c>
-      <c r="U437" t="inlineStr">
+      <c r="X437" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
@@ -25873,7 +25903,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U438" t="inlineStr">
+      <c r="X438" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -25931,7 +25961,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U439" t="inlineStr">
+      <c r="X439" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -25989,7 +26019,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U440" t="inlineStr">
+      <c r="X440" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -26047,7 +26077,7 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="U441" t="inlineStr">
+      <c r="X441" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -26105,7 +26135,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U442" t="inlineStr">
+      <c r="X442" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -26163,7 +26193,7 @@
           <t>COMBOT Sebastien</t>
         </is>
       </c>
-      <c r="U443" t="inlineStr">
+      <c r="X443" t="inlineStr">
         <is>
           <t>35234</t>
         </is>
@@ -26221,7 +26251,7 @@
           <t>WERRO Lukas</t>
         </is>
       </c>
-      <c r="U444" t="inlineStr">
+      <c r="X444" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
@@ -26279,7 +26309,7 @@
           <t>VIANELLO Marco</t>
         </is>
       </c>
-      <c r="U445" t="inlineStr">
+      <c r="X445" t="inlineStr">
         <is>
           <t>54910</t>
         </is>
@@ -26337,7 +26367,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U446" t="inlineStr">
+      <c r="X446" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -26395,7 +26425,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U447" t="inlineStr">
+      <c r="X447" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -26453,7 +26483,7 @@
           <t>OKREGLAK Maciej</t>
         </is>
       </c>
-      <c r="U448" t="inlineStr">
+      <c r="X448" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
@@ -26511,7 +26541,7 @@
           <t>BOWERS Christopher</t>
         </is>
       </c>
-      <c r="U449" t="inlineStr">
+      <c r="X449" t="inlineStr">
         <is>
           <t>52010</t>
         </is>
@@ -26569,7 +26599,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U450" t="inlineStr">
+      <c r="X450" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -26627,7 +26657,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U451" t="inlineStr">
+      <c r="X451" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -26685,7 +26715,7 @@
           <t>HRADILEK Vavrinec</t>
         </is>
       </c>
-      <c r="U452" t="inlineStr">
+      <c r="X452" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
@@ -26743,7 +26773,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U453" t="inlineStr">
+      <c r="X453" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -26801,7 +26831,7 @@
           <t>SRABOTNIK Martin</t>
         </is>
       </c>
-      <c r="U454" t="inlineStr">
+      <c r="X454" t="inlineStr">
         <is>
           <t>39080</t>
         </is>
@@ -26859,7 +26889,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U455" t="inlineStr">
+      <c r="X455" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -26917,7 +26947,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U456" t="inlineStr">
+      <c r="X456" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -26975,7 +27005,7 @@
           <t>SCHWEIKERT Fabian</t>
         </is>
       </c>
-      <c r="U457" t="inlineStr">
+      <c r="X457" t="inlineStr">
         <is>
           <t>38412</t>
         </is>
@@ -27033,7 +27063,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U458" t="inlineStr">
+      <c r="X458" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
@@ -27091,7 +27121,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U459" t="inlineStr">
+      <c r="X459" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -27149,7 +27179,7 @@
           <t>SCHUBERT Sebastian</t>
         </is>
       </c>
-      <c r="U460" t="inlineStr">
+      <c r="X460" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
@@ -27207,7 +27237,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U461" t="inlineStr">
+      <c r="X461" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -27265,7 +27295,7 @@
           <t>AIGNER Hannes</t>
         </is>
       </c>
-      <c r="U462" t="inlineStr">
+      <c r="X462" t="inlineStr">
         <is>
           <t>35115</t>
         </is>
@@ -27323,7 +27353,7 @@
           <t>IVALDI Zeno</t>
         </is>
       </c>
-      <c r="U463" t="inlineStr">
+      <c r="X463" t="inlineStr">
         <is>
           <t>35480</t>
         </is>
@@ -27381,7 +27411,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U464" t="inlineStr">
+      <c r="X464" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -27439,7 +27469,7 @@
           <t>GRIMM Alexander</t>
         </is>
       </c>
-      <c r="U465" t="inlineStr">
+      <c r="X465" t="inlineStr">
         <is>
           <t>35112</t>
         </is>
@@ -27512,12 +27542,12 @@
           <t>MUELLER Kevin</t>
         </is>
       </c>
-      <c r="U466" t="inlineStr">
+      <c r="X466" t="inlineStr">
         <is>
           <t>35148</t>
         </is>
       </c>
-      <c r="V466" t="inlineStr">
+      <c r="Y466" t="inlineStr">
         <is>
           <t>35149</t>
         </is>
@@ -27590,12 +27620,12 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U467" t="inlineStr">
+      <c r="X467" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
       </c>
-      <c r="V467" t="inlineStr">
+      <c r="Y467" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -27668,12 +27698,12 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="U468" t="inlineStr">
+      <c r="X468" t="inlineStr">
         <is>
           <t>35060</t>
         </is>
       </c>
-      <c r="V468" t="inlineStr">
+      <c r="Y468" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -27746,12 +27776,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U469" t="inlineStr">
+      <c r="X469" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V469" t="inlineStr">
+      <c r="Y469" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -27824,12 +27854,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U470" t="inlineStr">
+      <c r="X470" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V470" t="inlineStr">
+      <c r="Y470" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -27902,12 +27932,12 @@
           <t>SKANTAR Peter</t>
         </is>
       </c>
-      <c r="U471" t="inlineStr">
+      <c r="X471" t="inlineStr">
         <is>
           <t>35360</t>
         </is>
       </c>
-      <c r="V471" t="inlineStr">
+      <c r="Y471" t="inlineStr">
         <is>
           <t>35361</t>
         </is>
@@ -27980,12 +28010,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U472" t="inlineStr">
+      <c r="X472" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V472" t="inlineStr">
+      <c r="Y472" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -28058,12 +28088,12 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U473" t="inlineStr">
+      <c r="X473" t="inlineStr">
         <is>
           <t>35145</t>
         </is>
       </c>
-      <c r="V473" t="inlineStr">
+      <c r="Y473" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -28136,12 +28166,12 @@
           <t>BENZIEN Jan</t>
         </is>
       </c>
-      <c r="U474" t="inlineStr">
+      <c r="X474" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
       </c>
-      <c r="V474" t="inlineStr">
+      <c r="Y474" t="inlineStr">
         <is>
           <t>35134</t>
         </is>
@@ -28214,12 +28244,12 @@
           <t>CAILHOL Hugo</t>
         </is>
       </c>
-      <c r="U475" t="inlineStr">
+      <c r="X475" t="inlineStr">
         <is>
           <t>35476</t>
         </is>
       </c>
-      <c r="V475" t="inlineStr">
+      <c r="Y475" t="inlineStr">
         <is>
           <t>35491</t>
         </is>
@@ -28287,7 +28317,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U476" t="inlineStr">
+      <c r="X476" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -28418,7 +28448,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U478" t="inlineStr">
+      <c r="X478" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -28486,7 +28516,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U479" t="inlineStr">
+      <c r="X479" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -28554,7 +28584,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U480" t="inlineStr">
+      <c r="X480" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -28622,7 +28652,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U481" t="inlineStr">
+      <c r="X481" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -28690,7 +28720,7 @@
           <t>MUKHGALEEVA Polina</t>
         </is>
       </c>
-      <c r="U482" t="inlineStr">
+      <c r="X482" t="inlineStr">
         <is>
           <t>35768</t>
         </is>
@@ -28821,7 +28851,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U484" t="inlineStr">
+      <c r="X484" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -28889,7 +28919,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U485" t="inlineStr">
+      <c r="X485" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -28957,7 +28987,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U486" t="inlineStr">
+      <c r="X486" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -29025,7 +29055,7 @@
           <t>HRADILEK Vavrinec</t>
         </is>
       </c>
-      <c r="U487" t="inlineStr">
+      <c r="X487" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
@@ -29093,7 +29123,7 @@
           <t>IVALDI Zeno</t>
         </is>
       </c>
-      <c r="U488" t="inlineStr">
+      <c r="X488" t="inlineStr">
         <is>
           <t>35480</t>
         </is>
@@ -29161,7 +29191,7 @@
           <t>SCHUBERT Sebastian</t>
         </is>
       </c>
-      <c r="U489" t="inlineStr">
+      <c r="X489" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
@@ -29229,7 +29259,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U490" t="inlineStr">
+      <c r="X490" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -29297,7 +29327,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U491" t="inlineStr">
+      <c r="X491" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -29365,7 +29395,7 @@
           <t>COMBOT Sebastien</t>
         </is>
       </c>
-      <c r="U492" t="inlineStr">
+      <c r="X492" t="inlineStr">
         <is>
           <t>35234</t>
         </is>
@@ -29433,7 +29463,7 @@
           <t>ADACHI Kazuya</t>
         </is>
       </c>
-      <c r="U493" t="inlineStr">
+      <c r="X493" t="inlineStr">
         <is>
           <t>36646</t>
         </is>
@@ -29501,7 +29531,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U494" t="inlineStr">
+      <c r="X494" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -29569,7 +29599,7 @@
           <t>GRIMM Alexander</t>
         </is>
       </c>
-      <c r="U495" t="inlineStr">
+      <c r="X495" t="inlineStr">
         <is>
           <t>35112</t>
         </is>
@@ -29839,7 +29869,7 @@
           <t>PEROVA Aleksandra</t>
         </is>
       </c>
-      <c r="U500" t="inlineStr">
+      <c r="X500" t="inlineStr">
         <is>
           <t>35256</t>
         </is>
@@ -29897,7 +29927,7 @@
           <t>TROMPETER Caroline</t>
         </is>
       </c>
-      <c r="U501" t="inlineStr">
+      <c r="X501" t="inlineStr">
         <is>
           <t>39167</t>
         </is>
@@ -29955,7 +29985,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U502" t="inlineStr">
+      <c r="X502" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -30013,7 +30043,7 @@
           <t>REN Ye</t>
         </is>
       </c>
-      <c r="U503" t="inlineStr">
+      <c r="X503" t="inlineStr">
         <is>
           <t>68810</t>
         </is>
@@ -30071,7 +30101,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U504" t="inlineStr">
+      <c r="X504" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -30129,7 +30159,7 @@
           <t>GOIKOETXEA Irati</t>
         </is>
       </c>
-      <c r="U505" t="inlineStr">
+      <c r="X505" t="inlineStr">
         <is>
           <t>35761</t>
         </is>
@@ -30187,7 +30217,7 @@
           <t>KALISKA Elena</t>
         </is>
       </c>
-      <c r="U506" t="inlineStr">
+      <c r="X506" t="inlineStr">
         <is>
           <t>35366</t>
         </is>
@@ -30245,7 +30275,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U507" t="inlineStr">
+      <c r="X507" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -30303,7 +30333,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U508" t="inlineStr">
+      <c r="X508" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -30361,7 +30391,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U509" t="inlineStr">
+      <c r="X509" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -30419,7 +30449,7 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U510" t="inlineStr">
+      <c r="X510" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -30477,7 +30507,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U511" t="inlineStr">
+      <c r="X511" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -30535,7 +30565,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U512" t="inlineStr">
+      <c r="X512" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -30593,7 +30623,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U513" t="inlineStr">
+      <c r="X513" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -30651,7 +30681,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U514" t="inlineStr">
+      <c r="X514" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -30709,7 +30739,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U515" t="inlineStr">
+      <c r="X515" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -30767,7 +30797,7 @@
           <t>HILGERTOVA Stepanka</t>
         </is>
       </c>
-      <c r="U516" t="inlineStr">
+      <c r="X516" t="inlineStr">
         <is>
           <t>35035</t>
         </is>
@@ -30825,7 +30855,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U517" t="inlineStr">
+      <c r="X517" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -30883,7 +30913,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U518" t="inlineStr">
+      <c r="X518" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -30941,7 +30971,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U519" t="inlineStr">
+      <c r="X519" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -30999,7 +31029,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U520" t="inlineStr">
+      <c r="X520" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -31057,7 +31087,7 @@
           <t>PENNIE Fiona</t>
         </is>
       </c>
-      <c r="U521" t="inlineStr">
+      <c r="X521" t="inlineStr">
         <is>
           <t>35638</t>
         </is>
@@ -31115,7 +31145,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U522" t="inlineStr">
+      <c r="X522" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -31173,7 +31203,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U523" t="inlineStr">
+      <c r="X523" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -31231,7 +31261,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U524" t="inlineStr">
+      <c r="X524" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -31289,7 +31319,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U525" t="inlineStr">
+      <c r="X525" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -31347,7 +31377,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U526" t="inlineStr">
+      <c r="X526" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -31405,7 +31435,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U527" t="inlineStr">
+      <c r="X527" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -31463,7 +31493,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U528" t="inlineStr">
+      <c r="X528" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -31521,7 +31551,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U529" t="inlineStr">
+      <c r="X529" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -31579,7 +31609,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U530" t="inlineStr">
+      <c r="X530" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -31637,7 +31667,7 @@
           <t>SASAKI Shota</t>
         </is>
       </c>
-      <c r="U531" t="inlineStr">
+      <c r="X531" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -31695,7 +31725,7 @@
           <t>BORROWS Ian</t>
         </is>
       </c>
-      <c r="U532" t="inlineStr">
+      <c r="X532" t="inlineStr">
         <is>
           <t>36534</t>
         </is>
@@ -31753,7 +31783,7 @@
           <t>SZTUBA Kacper</t>
         </is>
       </c>
-      <c r="U533" t="inlineStr">
+      <c r="X533" t="inlineStr">
         <is>
           <t>53636</t>
         </is>
@@ -31811,7 +31841,7 @@
           <t>MARC Jonathan</t>
         </is>
       </c>
-      <c r="U534" t="inlineStr">
+      <c r="X534" t="inlineStr">
         <is>
           <t>35388</t>
         </is>
@@ -31869,7 +31899,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U535" t="inlineStr">
+      <c r="X535" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -31927,7 +31957,7 @@
           <t>SETKIN Kirill</t>
         </is>
       </c>
-      <c r="U536" t="inlineStr">
+      <c r="X536" t="inlineStr">
         <is>
           <t>35457</t>
         </is>
@@ -31985,7 +32015,7 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U537" t="inlineStr">
+      <c r="X537" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -32043,7 +32073,7 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U538" t="inlineStr">
+      <c r="X538" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -32101,7 +32131,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U539" t="inlineStr">
+      <c r="X539" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -32159,7 +32189,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U540" t="inlineStr">
+      <c r="X540" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -32217,7 +32247,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U541" t="inlineStr">
+      <c r="X541" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -32275,7 +32305,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U542" t="inlineStr">
+      <c r="X542" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -32333,7 +32363,7 @@
           <t>BADURA Jergus</t>
         </is>
       </c>
-      <c r="U543" t="inlineStr">
+      <c r="X543" t="inlineStr">
         <is>
           <t>68767</t>
         </is>
@@ -32391,7 +32421,7 @@
           <t>JANE Michal</t>
         </is>
       </c>
-      <c r="U544" t="inlineStr">
+      <c r="X544" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
@@ -32449,7 +32479,7 @@
           <t>HANEDA Takuya</t>
         </is>
       </c>
-      <c r="U545" t="inlineStr">
+      <c r="X545" t="inlineStr">
         <is>
           <t>36481</t>
         </is>
@@ -32507,7 +32537,7 @@
           <t>COLAZINGARI Roberto</t>
         </is>
       </c>
-      <c r="U546" t="inlineStr">
+      <c r="X546" t="inlineStr">
         <is>
           <t>35223</t>
         </is>
@@ -32565,7 +32595,7 @@
           <t>ELOSEGI Ander</t>
         </is>
       </c>
-      <c r="U547" t="inlineStr">
+      <c r="X547" t="inlineStr">
         <is>
           <t>35785</t>
         </is>
@@ -32623,7 +32653,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U548" t="inlineStr">
+      <c r="X548" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -32681,7 +32711,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U549" t="inlineStr">
+      <c r="X549" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -32739,7 +32769,7 @@
           <t>ROHAN Lukas</t>
         </is>
       </c>
-      <c r="U550" t="inlineStr">
+      <c r="X550" t="inlineStr">
         <is>
           <t>36114</t>
         </is>
@@ -32797,7 +32827,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U551" t="inlineStr">
+      <c r="X551" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -32855,7 +32885,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U552" t="inlineStr">
+      <c r="X552" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -32913,7 +32943,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U553" t="inlineStr">
+      <c r="X553" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -32971,7 +33001,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U554" t="inlineStr">
+      <c r="X554" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -33029,7 +33059,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U555" t="inlineStr">
+      <c r="X555" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
@@ -33087,7 +33117,7 @@
           <t>FLORENCE David</t>
         </is>
       </c>
-      <c r="U556" t="inlineStr">
+      <c r="X556" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -33145,7 +33175,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U557" t="inlineStr">
+      <c r="X557" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -33203,7 +33233,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U558" t="inlineStr">
+      <c r="X558" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -33261,7 +33291,7 @@
           <t>GARGAUD CHANUT Denis</t>
         </is>
       </c>
-      <c r="U559" t="inlineStr">
+      <c r="X559" t="inlineStr">
         <is>
           <t>35177</t>
         </is>
@@ -33329,7 +33359,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U560" t="inlineStr">
+      <c r="X560" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -33397,7 +33427,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U561" t="inlineStr">
+      <c r="X561" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -33465,7 +33495,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U562" t="inlineStr">
+      <c r="X562" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -33533,7 +33563,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U563" t="inlineStr">
+      <c r="X563" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -33601,7 +33631,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U564" t="inlineStr">
+      <c r="X564" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -33669,7 +33699,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U565" t="inlineStr">
+      <c r="X565" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -33737,7 +33767,7 @@
           <t>PENNIE Fiona</t>
         </is>
       </c>
-      <c r="U566" t="inlineStr">
+      <c r="X566" t="inlineStr">
         <is>
           <t>35638</t>
         </is>
@@ -33805,7 +33835,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U567" t="inlineStr">
+      <c r="X567" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -33873,7 +33903,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U568" t="inlineStr">
+      <c r="X568" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -33941,7 +33971,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U569" t="inlineStr">
+      <c r="X569" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -34009,7 +34039,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U570" t="inlineStr">
+      <c r="X570" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -34077,7 +34107,7 @@
           <t>BADURA Jergus</t>
         </is>
       </c>
-      <c r="U571" t="inlineStr">
+      <c r="X571" t="inlineStr">
         <is>
           <t>68767</t>
         </is>
@@ -34145,7 +34175,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U572" t="inlineStr">
+      <c r="X572" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -34213,7 +34243,7 @@
           <t>GARGAUD CHANUT Denis</t>
         </is>
       </c>
-      <c r="U573" t="inlineStr">
+      <c r="X573" t="inlineStr">
         <is>
           <t>35177</t>
         </is>
@@ -34281,7 +34311,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U574" t="inlineStr">
+      <c r="X574" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -34349,7 +34379,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U575" t="inlineStr">
+      <c r="X575" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
@@ -34417,7 +34447,7 @@
           <t>ROHAN Lukas</t>
         </is>
       </c>
-      <c r="U576" t="inlineStr">
+      <c r="X576" t="inlineStr">
         <is>
           <t>36114</t>
         </is>
@@ -34485,7 +34515,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U577" t="inlineStr">
+      <c r="X577" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -34553,7 +34583,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U578" t="inlineStr">
+      <c r="X578" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -34621,7 +34651,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U579" t="inlineStr">
+      <c r="X579" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
